--- a/psychopy_exp_files/sequences/learning_block4_fixed-middle-10_39.xlsx
+++ b/psychopy_exp_files/sequences/learning_block4_fixed-middle-10_39.xlsx
@@ -767,17 +767,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_11.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_25.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>stimuli/house/house_10.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -787,17 +787,17 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -833,13 +833,13 @@
         <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="W4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -861,17 +861,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_11.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_09.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_04.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -881,17 +881,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -929,13 +929,13 @@
         <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="V5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W5" t="n">
         <v>11</v>
@@ -960,42 +960,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_04.jpg</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_25.jpg</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_10.jpg</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_04.jpg</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_21.jpg</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_10.jpg</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>hammer</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>house</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1028,16 +1028,16 @@
         <v>6</v>
       </c>
       <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
+      </c>
+      <c r="V6" t="n">
+        <v>9</v>
+      </c>
+      <c r="W6" t="n">
         <v>7</v>
-      </c>
-      <c r="U6" t="n">
-        <v>4</v>
-      </c>
-      <c r="V6" t="n">
-        <v>6</v>
-      </c>
-      <c r="W6" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_04.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1074,12 +1074,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_11.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1127,7 +1127,7 @@
         <v>7</v>
       </c>
       <c r="T7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U7" t="n">
         <v>8</v>
@@ -1136,7 +1136,7 @@
         <v>14</v>
       </c>
       <c r="W7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -1163,12 +1163,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>stimuli/house/house_10.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1229,10 +1229,10 @@
         <v>8</v>
       </c>
       <c r="U8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W8" t="n">
         <v>12</v>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_21.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1272,17 +1272,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_09.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1325,16 +1325,16 @@
         <v>9</v>
       </c>
       <c r="T9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V9" t="n">
         <v>13</v>
       </c>
       <c r="W9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -1356,12 +1356,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_21.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_25.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1424,10 +1424,10 @@
         <v>10</v>
       </c>
       <c r="T10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U10" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="V10" t="n">
         <v>11</v>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_25.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1470,12 +1470,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1523,7 +1523,7 @@
         <v>11</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U11" t="n">
         <v>1</v>
@@ -1532,7 +1532,7 @@
         <v>14</v>
       </c>
       <c r="W11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>stimuli/house/house_10.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1625,7 +1625,7 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V12" t="n">
         <v>12</v>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>stimuli/house/house_10.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_04.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1721,7 +1721,7 @@
         <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U13" t="n">
         <v>11</v>
@@ -1730,7 +1730,7 @@
         <v>14</v>
       </c>
       <c r="W13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_25.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1829,7 +1829,7 @@
         <v>2</v>
       </c>
       <c r="W14" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>stimuli/house/house_05.jpg</t>
+          <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1925,7 +1925,7 @@
         <v>17</v>
       </c>
       <c r="V15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W15" t="n">
         <v>12</v>
@@ -1960,12 +1960,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_16.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_30.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2024,10 +2024,10 @@
         <v>8</v>
       </c>
       <c r="V16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2123,7 +2123,7 @@
         <v>1</v>
       </c>
       <c r="V17" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="W17" t="n">
         <v>12</v>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_16.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2222,7 +2222,7 @@
         <v>2</v>
       </c>
       <c r="V18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W18" t="n">
         <v>13</v>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_35.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2318,7 +2318,7 @@
         <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V19" t="n">
         <v>13</v>
@@ -2346,17 +2346,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_35.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_16.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_22.jpg</t>
+          <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2366,17 +2366,17 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2414,13 +2414,13 @@
         <v>7</v>
       </c>
       <c r="T20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V20" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W20" t="n">
         <v>12</v>
@@ -2445,19 +2445,19 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_49.jpg</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>stimuli/jacket/jacket_35.jpg</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_16.jpg</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_49.jpg</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
-        </is>
-      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>stimuli/glasses/glasses_06.jpg</t>
@@ -2465,17 +2465,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t>chair</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>hammer</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2513,13 +2513,13 @@
         <v>8</v>
       </c>
       <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>10</v>
+      </c>
+      <c r="V21" t="n">
         <v>4</v>
-      </c>
-      <c r="U21" t="n">
-        <v>3</v>
-      </c>
-      <c r="V21" t="n">
-        <v>7</v>
       </c>
       <c r="W21" t="n">
         <v>18</v>
@@ -2544,42 +2544,42 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_16.jpg</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_05.jpg</t>
-        </is>
-      </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_35.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t>hammer</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2612,16 +2612,16 @@
         <v>9</v>
       </c>
       <c r="T22" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U22" t="n">
+        <v>4</v>
+      </c>
+      <c r="V22" t="n">
         <v>7</v>
       </c>
-      <c r="V22" t="n">
-        <v>9</v>
-      </c>
       <c r="W22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
@@ -2643,19 +2643,19 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_16.jpg</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_22.jpg</t>
-        </is>
-      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>stimuli/phone/phone_29.jpg</t>
@@ -2663,17 +2663,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
           <t>hammer</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>house</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2711,13 +2711,13 @@
         <v>10</v>
       </c>
       <c r="T23" t="n">
+        <v>4</v>
+      </c>
+      <c r="U23" t="n">
         <v>7</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>9</v>
-      </c>
-      <c r="V23" t="n">
-        <v>6</v>
       </c>
       <c r="W23" t="n">
         <v>17</v>
@@ -2742,14 +2742,14 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_26.jpg</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
           <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_22.jpg</t>
-        </is>
-      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>stimuli/hand/hand_30.jpg</t>
@@ -2762,12 +2762,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
           <t>house</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2810,10 +2810,10 @@
         <v>11</v>
       </c>
       <c r="T24" t="n">
+        <v>7</v>
+      </c>
+      <c r="U24" t="n">
         <v>9</v>
-      </c>
-      <c r="U24" t="n">
-        <v>6</v>
       </c>
       <c r="V24" t="n">
         <v>8</v>
@@ -2841,14 +2841,14 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>stimuli/house/house_05.jpg</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_30.jpg</t>
-        </is>
-      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>stimuli/ball/ball_23.jpg</t>
@@ -2856,19 +2856,19 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
           <t>flower</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>ball</t>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2909,16 +2909,16 @@
         <v>12</v>
       </c>
       <c r="T25" t="n">
+        <v>9</v>
+      </c>
+      <c r="U25" t="n">
         <v>6</v>
-      </c>
-      <c r="U25" t="n">
-        <v>5</v>
       </c>
       <c r="V25" t="n">
         <v>1</v>
       </c>
       <c r="W25" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
@@ -2940,42 +2940,42 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_22.jpg</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>stimuli/glasses/glasses_06.jpg</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>stimuli/phone/phone_29.jpg</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>stimuli/glasses/glasses_06.jpg</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>stimuli/phone/phone_29.jpg</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_35.jpg</t>
-        </is>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>glasses</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>phone</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t>dog</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>glasses</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>jacket</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3008,7 +3008,7 @@
         <v>13</v>
       </c>
       <c r="T26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U26" t="n">
         <v>18</v>
@@ -3017,7 +3017,7 @@
         <v>17</v>
       </c>
       <c r="W26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/chair/chair_16.jpg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3116,7 +3116,7 @@
         <v>8</v>
       </c>
       <c r="W27" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_21.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3212,7 +3212,7 @@
         <v>12</v>
       </c>
       <c r="V28" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W28" t="n">
         <v>13</v>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_04.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>stimuli/house/house_10.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3311,10 +3311,10 @@
         <v>2</v>
       </c>
       <c r="V29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W29" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_11.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3407,7 +3407,7 @@
         <v>2</v>
       </c>
       <c r="U30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V30" t="n">
         <v>8</v>
@@ -3435,17 +3435,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_11.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_09.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_21.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3455,17 +3455,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3503,13 +3503,13 @@
         <v>5</v>
       </c>
       <c r="T31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U31" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="V31" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W31" t="n">
         <v>11</v>
@@ -3534,42 +3534,42 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_04.jpg</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_25.jpg</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>stimuli/jacket/jacket_06.jpg</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_04.jpg</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_25.jpg</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_10.jpg</t>
-        </is>
-      </c>
       <c r="I32" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t>hammer</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>house</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>6</v>
       </c>
       <c r="T32" t="n">
+        <v>4</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
+      </c>
+      <c r="V32" t="n">
+        <v>10</v>
+      </c>
+      <c r="W32" t="n">
         <v>7</v>
-      </c>
-      <c r="U32" t="n">
-        <v>4</v>
-      </c>
-      <c r="V32" t="n">
-        <v>3</v>
-      </c>
-      <c r="W32" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="33">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_04.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_21.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3701,13 +3701,13 @@
         <v>7</v>
       </c>
       <c r="T33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U33" t="n">
         <v>8</v>
       </c>
       <c r="V33" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W33" t="n">
         <v>1</v>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_11.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3803,13 +3803,13 @@
         <v>8</v>
       </c>
       <c r="U34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V34" t="n">
         <v>13</v>
       </c>
       <c r="W34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_21.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3846,17 +3846,17 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_09.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3899,16 +3899,16 @@
         <v>9</v>
       </c>
       <c r="T35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U35" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="V35" t="n">
         <v>14</v>
       </c>
       <c r="W35" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36">
@@ -3930,42 +3930,42 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
+          <t>stimuli/house/house_10.jpg</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>stimuli/jacket/jacket_06.jpg</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>stimuli/fish/fish_12.jpg</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_25.jpg</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>stimuli/fish/fish_12.jpg</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_11.jpg</t>
-        </is>
-      </c>
       <c r="I36" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fish</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fish</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>dog</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3998,16 +3998,16 @@
         <v>10</v>
       </c>
       <c r="T36" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U36" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="V36" t="n">
         <v>12</v>
       </c>
       <c r="W36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
@@ -4029,42 +4029,42 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_06.jpg</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>stimuli/ball/ball_04.jpg</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_04.jpg</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_04.jpg</t>
-        </is>
-      </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t>bread</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4097,16 +4097,16 @@
         <v>11</v>
       </c>
       <c r="T37" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U37" t="n">
         <v>1</v>
       </c>
       <c r="V37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>stimuli/house/house_10.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -4199,7 +4199,7 @@
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V38" t="n">
         <v>2</v>
@@ -4227,42 +4227,42 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_09.jpg</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>stimuli/car/car_10.jpg</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>stimuli/lamp/lamp_40.jpg</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
           <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>stimuli/car/car_10.jpg</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>stimuli/lamp/lamp_40.jpg</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_21.jpg</t>
-        </is>
-      </c>
       <c r="I39" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>car</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>lamp</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
           <t>house</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>car</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>lamp</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4295,7 +4295,7 @@
         <v>13</v>
       </c>
       <c r="T39" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U39" t="n">
         <v>11</v>
@@ -4304,7 +4304,7 @@
         <v>14</v>
       </c>
       <c r="W39" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4403,7 +4403,7 @@
         <v>12</v>
       </c>
       <c r="W40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
@@ -4435,7 +4435,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_22.jpg</t>
+          <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4499,7 +4499,7 @@
         <v>17</v>
       </c>
       <c r="V41" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W41" t="n">
         <v>12</v>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>stimuli/house/house_05.jpg</t>
+          <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4601,7 +4601,7 @@
         <v>1</v>
       </c>
       <c r="W42" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43">
@@ -4633,12 +4633,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_35.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_30.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4697,10 +4697,10 @@
         <v>1</v>
       </c>
       <c r="V43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_16.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4796,7 +4796,7 @@
         <v>2</v>
       </c>
       <c r="V44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W44" t="n">
         <v>12</v>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_35.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/chair/chair_16.jpg</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4846,12 +4846,12 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4892,10 +4892,10 @@
         <v>2</v>
       </c>
       <c r="U45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V45" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="W45" t="n">
         <v>18</v>
@@ -4920,12 +4920,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_35.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_16.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4988,10 +4988,10 @@
         <v>7</v>
       </c>
       <c r="T46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V46" t="n">
         <v>13</v>
@@ -5019,12 +5019,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_16.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -5087,10 +5087,10 @@
         <v>8</v>
       </c>
       <c r="T47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U47" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="V47" t="n">
         <v>12</v>
@@ -5118,19 +5118,19 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_16.jpg</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_05.jpg</t>
-        </is>
-      </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>stimuli/hand/hand_30.jpg</t>
@@ -5138,17 +5138,17 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t>hammer</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>house</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -5186,13 +5186,13 @@
         <v>9</v>
       </c>
       <c r="T48" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U48" t="n">
+        <v>4</v>
+      </c>
+      <c r="V48" t="n">
         <v>7</v>
-      </c>
-      <c r="V48" t="n">
-        <v>9</v>
       </c>
       <c r="W48" t="n">
         <v>8</v>
@@ -5217,14 +5217,14 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_16.jpg</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_05.jpg</t>
-        </is>
-      </c>
       <c r="G49" t="inlineStr">
         <is>
           <t>stimuli/guitar/guitar_32.jpg</t>
@@ -5237,12 +5237,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
           <t>hammer</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>house</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -5285,10 +5285,10 @@
         <v>10</v>
       </c>
       <c r="T49" t="n">
+        <v>4</v>
+      </c>
+      <c r="U49" t="n">
         <v>7</v>
-      </c>
-      <c r="U49" t="n">
-        <v>9</v>
       </c>
       <c r="V49" t="n">
         <v>13</v>
@@ -5316,14 +5316,14 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_26.jpg</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_22.jpg</t>
-        </is>
-      </c>
       <c r="G50" t="inlineStr">
         <is>
           <t>stimuli/bicycle/bicycle_35.jpg</t>
@@ -5331,19 +5331,19 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
       <c r="K50" t="inlineStr">
         <is>
           <t>bicycle</t>
@@ -5351,7 +5351,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5384,16 +5384,16 @@
         <v>11</v>
       </c>
       <c r="T50" t="n">
+        <v>7</v>
+      </c>
+      <c r="U50" t="n">
         <v>9</v>
-      </c>
-      <c r="U50" t="n">
-        <v>6</v>
       </c>
       <c r="V50" t="n">
         <v>2</v>
       </c>
       <c r="W50" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51">
@@ -5415,42 +5415,42 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
+          <t>stimuli/house/house_05.jpg</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>stimuli/guitar/guitar_32.jpg</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
         <is>
           <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>stimuli/guitar/guitar_32.jpg</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_35.jpg</t>
-        </is>
-      </c>
       <c r="I51" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
           <t>flower</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>guitar</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
         <is>
           <t>dog</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>guitar</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>jacket</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5483,16 +5483,16 @@
         <v>12</v>
       </c>
       <c r="T51" t="n">
+        <v>9</v>
+      </c>
+      <c r="U51" t="n">
         <v>6</v>
-      </c>
-      <c r="U51" t="n">
-        <v>5</v>
       </c>
       <c r="V51" t="n">
         <v>13</v>
       </c>
       <c r="W51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_30.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -5582,7 +5582,7 @@
         <v>13</v>
       </c>
       <c r="T52" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U52" t="n">
         <v>18</v>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_16.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5687,7 +5687,7 @@
         <v>12</v>
       </c>
       <c r="V53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W53" t="n">
         <v>13</v>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>stimuli/house/house_10.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -5786,7 +5786,7 @@
         <v>12</v>
       </c>
       <c r="V54" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W54" t="n">
         <v>13</v>
@@ -5821,12 +5821,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_11.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>stimuli/house/house_10.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5885,10 +5885,10 @@
         <v>2</v>
       </c>
       <c r="V55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W55" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56">
@@ -5915,12 +5915,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_11.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_21.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5981,10 +5981,10 @@
         <v>2</v>
       </c>
       <c r="U56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V56" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W56" t="n">
         <v>11</v>
@@ -6009,12 +6009,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_11.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_09.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -6077,10 +6077,10 @@
         <v>5</v>
       </c>
       <c r="T57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U57" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="V57" t="n">
         <v>1</v>
@@ -6108,17 +6108,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_09.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_04.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6128,17 +6128,17 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -6176,13 +6176,13 @@
         <v>6</v>
       </c>
       <c r="T58" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W58" t="n">
         <v>11</v>
@@ -6207,7 +6207,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_04.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6217,17 +6217,17 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_25.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>stimuli/house/house_10.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6275,16 +6275,16 @@
         <v>7</v>
       </c>
       <c r="T59" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U59" t="n">
         <v>8</v>
       </c>
       <c r="V59" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="W59" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60">
@@ -6311,17 +6311,17 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>stimuli/house/house_10.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_09.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -6331,17 +6331,17 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6377,13 +6377,13 @@
         <v>8</v>
       </c>
       <c r="U60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V60" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W60" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
@@ -6405,42 +6405,42 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_11.jpg</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_10.jpg</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_21.jpg</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_04.jpg</t>
-        </is>
-      </c>
       <c r="I61" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t>jacket</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>bread</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>chair</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6473,16 +6473,16 @@
         <v>9</v>
       </c>
       <c r="T61" t="n">
+        <v>5</v>
+      </c>
+      <c r="U61" t="n">
+        <v>9</v>
+      </c>
+      <c r="V61" t="n">
         <v>10</v>
       </c>
-      <c r="U61" t="n">
-        <v>6</v>
-      </c>
-      <c r="V61" t="n">
+      <c r="W61" t="n">
         <v>3</v>
-      </c>
-      <c r="W61" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="62">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_21.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_25.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -6572,10 +6572,10 @@
         <v>10</v>
       </c>
       <c r="T62" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U62" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="V62" t="n">
         <v>14</v>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_25.jpg</t>
+          <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -6671,7 +6671,7 @@
         <v>11</v>
       </c>
       <c r="T63" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U63" t="n">
         <v>1</v>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>stimuli/house/house_10.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_04.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6727,7 +6727,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -6773,13 +6773,13 @@
         <v>1</v>
       </c>
       <c r="U64" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V64" t="n">
         <v>2</v>
       </c>
       <c r="W64" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>stimuli/house/house_10.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -6811,17 +6811,17 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_09.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -6869,16 +6869,16 @@
         <v>13</v>
       </c>
       <c r="T65" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U65" t="n">
         <v>11</v>
       </c>
       <c r="V65" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="W65" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_21.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6935,7 +6935,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -6977,7 +6977,7 @@
         <v>12</v>
       </c>
       <c r="W66" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/chair/chair_16.jpg</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -7172,7 +7172,7 @@
         <v>8</v>
       </c>
       <c r="V68" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="W68" t="n">
         <v>12</v>
@@ -7207,7 +7207,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_22.jpg</t>
+          <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7227,7 +7227,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -7271,7 +7271,7 @@
         <v>1</v>
       </c>
       <c r="V69" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W69" t="n">
         <v>18</v>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -7370,7 +7370,7 @@
         <v>2</v>
       </c>
       <c r="V70" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="W70" t="n">
         <v>12</v>
@@ -7400,12 +7400,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_35.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_16.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -7466,10 +7466,10 @@
         <v>2</v>
       </c>
       <c r="U71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V71" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W71" t="n">
         <v>18</v>
@@ -7494,42 +7494,42 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_35.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_49.jpg</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_16.jpg</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
-        </is>
-      </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_30.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t>chair</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -7562,16 +7562,16 @@
         <v>7</v>
       </c>
       <c r="T72" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U72" t="n">
+        <v>3</v>
+      </c>
+      <c r="V72" t="n">
         <v>4</v>
       </c>
-      <c r="V72" t="n">
-        <v>7</v>
-      </c>
       <c r="W72" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_16.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -7661,10 +7661,10 @@
         <v>8</v>
       </c>
       <c r="T73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U73" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="V73" t="n">
         <v>17</v>
@@ -7692,19 +7692,19 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_16.jpg</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_05.jpg</t>
-        </is>
-      </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>stimuli/fish/fish_01.jpg</t>
@@ -7712,17 +7712,17 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t>hammer</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>house</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -7760,13 +7760,13 @@
         <v>9</v>
       </c>
       <c r="T74" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U74" t="n">
+        <v>4</v>
+      </c>
+      <c r="V74" t="n">
         <v>7</v>
-      </c>
-      <c r="V74" t="n">
-        <v>9</v>
       </c>
       <c r="W74" t="n">
         <v>12</v>
@@ -7791,14 +7791,14 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_16.jpg</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_05.jpg</t>
-        </is>
-      </c>
       <c r="G75" t="inlineStr">
         <is>
           <t>stimuli/hand/hand_30.jpg</t>
@@ -7811,12 +7811,12 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
           <t>hammer</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>house</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -7859,10 +7859,10 @@
         <v>10</v>
       </c>
       <c r="T75" t="n">
+        <v>4</v>
+      </c>
+      <c r="U75" t="n">
         <v>7</v>
-      </c>
-      <c r="U75" t="n">
-        <v>9</v>
       </c>
       <c r="V75" t="n">
         <v>8</v>
@@ -7890,14 +7890,14 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_26.jpg</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_22.jpg</t>
-        </is>
-      </c>
       <c r="G76" t="inlineStr">
         <is>
           <t>stimuli/phone/phone_29.jpg</t>
@@ -7905,19 +7905,19 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_35.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
           <t>house</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
       <c r="K76" t="inlineStr">
         <is>
           <t>phone</t>
@@ -7925,7 +7925,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -7958,16 +7958,16 @@
         <v>11</v>
       </c>
       <c r="T76" t="n">
+        <v>7</v>
+      </c>
+      <c r="U76" t="n">
         <v>9</v>
-      </c>
-      <c r="U76" t="n">
-        <v>6</v>
       </c>
       <c r="V76" t="n">
         <v>17</v>
       </c>
       <c r="W76" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77">
@@ -7989,14 +7989,14 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
+          <t>stimuli/house/house_05.jpg</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_30.jpg</t>
-        </is>
-      </c>
       <c r="G77" t="inlineStr">
         <is>
           <t>stimuli/guitar/guitar_32.jpg</t>
@@ -8009,12 +8009,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>dog</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -8057,10 +8057,10 @@
         <v>12</v>
       </c>
       <c r="T77" t="n">
+        <v>9</v>
+      </c>
+      <c r="U77" t="n">
         <v>6</v>
-      </c>
-      <c r="U77" t="n">
-        <v>5</v>
       </c>
       <c r="V77" t="n">
         <v>13</v>
@@ -8088,42 +8088,42 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_22.jpg</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>stimuli/glasses/glasses_06.jpg</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_30.jpg</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>stimuli/glasses/glasses_06.jpg</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_30.jpg</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_35.jpg</t>
-        </is>
-      </c>
       <c r="I78" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>glasses</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
           <t>dog</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>glasses</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>jacket</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8156,7 +8156,7 @@
         <v>13</v>
       </c>
       <c r="T78" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U78" t="n">
         <v>18</v>
@@ -8165,7 +8165,7 @@
         <v>8</v>
       </c>
       <c r="W78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_11.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -8316,7 +8316,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -8360,7 +8360,7 @@
         <v>12</v>
       </c>
       <c r="V80" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W80" t="n">
         <v>13</v>
@@ -8395,7 +8395,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_09.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8459,7 +8459,7 @@
         <v>2</v>
       </c>
       <c r="V81" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="W81" t="n">
         <v>11</v>
@@ -8489,12 +8489,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_11.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_21.jpg</t>
+          <t>stimuli/house/house_10.jpg</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -8509,12 +8509,12 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -8555,10 +8555,10 @@
         <v>2</v>
       </c>
       <c r="U82" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V82" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W82" t="n">
         <v>13</v>
@@ -8583,19 +8583,19 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_21.jpg</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>stimuli/chair/chair_04.jpg</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_09.jpg</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
-        </is>
-      </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>stimuli/car/car_10.jpg</t>
@@ -8603,17 +8603,17 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t>dog</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>jacket</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -8651,13 +8651,13 @@
         <v>5</v>
       </c>
       <c r="T83" t="n">
+        <v>6</v>
+      </c>
+      <c r="U83" t="n">
+        <v>4</v>
+      </c>
+      <c r="V83" t="n">
         <v>5</v>
-      </c>
-      <c r="U83" t="n">
-        <v>7</v>
-      </c>
-      <c r="V83" t="n">
-        <v>10</v>
       </c>
       <c r="W83" t="n">
         <v>11</v>
@@ -8682,12 +8682,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_09.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_04.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -8702,12 +8702,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -8750,10 +8750,10 @@
         <v>6</v>
       </c>
       <c r="T84" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U84" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V84" t="n">
         <v>14</v>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_04.jpg</t>
+          <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -8796,12 +8796,12 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_11.jpg</t>
+          <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -8849,7 +8849,7 @@
         <v>7</v>
       </c>
       <c r="T85" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U85" t="n">
         <v>8</v>
@@ -8858,7 +8858,7 @@
         <v>12</v>
       </c>
       <c r="W85" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86">
@@ -8885,12 +8885,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>stimuli/house/house_10.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -8951,10 +8951,10 @@
         <v>8</v>
       </c>
       <c r="U86" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V86" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W86" t="n">
         <v>13</v>
@@ -8979,19 +8979,19 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_11.jpg</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>stimuli/house/house_10.jpg</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_06.jpg</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_21.jpg</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_25.jpg</t>
-        </is>
-      </c>
       <c r="H87" t="inlineStr">
         <is>
           <t>stimuli/car/car_10.jpg</t>
@@ -8999,17 +8999,17 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t>jacket</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>flower</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>bread</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -9047,13 +9047,13 @@
         <v>9</v>
       </c>
       <c r="T87" t="n">
+        <v>5</v>
+      </c>
+      <c r="U87" t="n">
+        <v>9</v>
+      </c>
+      <c r="V87" t="n">
         <v>10</v>
-      </c>
-      <c r="U87" t="n">
-        <v>6</v>
-      </c>
-      <c r="V87" t="n">
-        <v>3</v>
       </c>
       <c r="W87" t="n">
         <v>11</v>
@@ -9078,19 +9078,19 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
+          <t>stimuli/house/house_10.jpg</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>stimuli/jacket/jacket_06.jpg</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_21.jpg</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_25.jpg</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_11.jpg</t>
-        </is>
-      </c>
       <c r="H88" t="inlineStr">
         <is>
           <t>stimuli/hand/hand_20.jpg</t>
@@ -9098,17 +9098,17 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>dog</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -9146,13 +9146,13 @@
         <v>10</v>
       </c>
       <c r="T88" t="n">
+        <v>9</v>
+      </c>
+      <c r="U88" t="n">
+        <v>10</v>
+      </c>
+      <c r="V88" t="n">
         <v>6</v>
-      </c>
-      <c r="U88" t="n">
-        <v>3</v>
-      </c>
-      <c r="V88" t="n">
-        <v>5</v>
       </c>
       <c r="W88" t="n">
         <v>8</v>
@@ -9177,42 +9177,42 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_06.jpg</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>stimuli/ball/ball_04.jpg</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_25.jpg</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_04.jpg</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_04.jpg</t>
-        </is>
-      </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_06.jpg</t>
+          <t>stimuli/dog/dog_11.jpg</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t>bread</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>chair</t>
-        </is>
-      </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -9245,16 +9245,16 @@
         <v>11</v>
       </c>
       <c r="T89" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U89" t="n">
         <v>1</v>
       </c>
       <c r="V89" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W89" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>stimuli/house/house_10.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -9347,7 +9347,7 @@
         <v>1</v>
       </c>
       <c r="U90" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V90" t="n">
         <v>13</v>
@@ -9375,7 +9375,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>stimuli/house/house_10.jpg</t>
+          <t>stimuli/hammer/hammer_09.jpg</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -9390,12 +9390,12 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_09.jpg</t>
+          <t>stimuli/chair/chair_04.jpg</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -9443,7 +9443,7 @@
         <v>13</v>
       </c>
       <c r="T91" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U91" t="n">
         <v>11</v>
@@ -9452,7 +9452,7 @@
         <v>14</v>
       </c>
       <c r="W91" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92">
@@ -9682,7 +9682,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_22.jpg</t>
+          <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -9702,7 +9702,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -9746,7 +9746,7 @@
         <v>8</v>
       </c>
       <c r="V94" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W94" t="n">
         <v>12</v>
@@ -9781,7 +9781,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -9845,7 +9845,7 @@
         <v>1</v>
       </c>
       <c r="V95" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="W95" t="n">
         <v>18</v>
@@ -9880,7 +9880,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_16.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -9900,7 +9900,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -9944,7 +9944,7 @@
         <v>2</v>
       </c>
       <c r="V96" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W96" t="n">
         <v>13</v>
@@ -9974,12 +9974,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_35.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_30.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -9994,12 +9994,12 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -10040,10 +10040,10 @@
         <v>2</v>
       </c>
       <c r="U97" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="V97" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W97" t="n">
         <v>12</v>
@@ -10068,17 +10068,17 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_35.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_16.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>stimuli/house/house_05.jpg</t>
+          <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -10088,17 +10088,17 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>house</t>
+          <t>hammer</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -10136,13 +10136,13 @@
         <v>7</v>
       </c>
       <c r="T98" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="U98" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V98" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W98" t="n">
         <v>18</v>
@@ -10167,12 +10167,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_16.jpg</t>
+          <t>stimuli/bread/bread_49.jpg</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -10187,12 +10187,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -10235,10 +10235,10 @@
         <v>8</v>
       </c>
       <c r="T99" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U99" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="V99" t="n">
         <v>12</v>
@@ -10266,17 +10266,17 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/chair/chair_16.jpg</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_22.jpg</t>
+          <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -10286,17 +10286,17 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>house</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -10334,13 +10334,13 @@
         <v>9</v>
       </c>
       <c r="T100" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="U100" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="V100" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="W100" t="n">
         <v>2</v>
@@ -10365,14 +10365,14 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_16.jpg</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
           <t>stimuli/hammer/hammer_26.jpg</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>stimuli/house/house_05.jpg</t>
-        </is>
-      </c>
       <c r="G101" t="inlineStr">
         <is>
           <t>stimuli/ball/ball_23.jpg</t>
@@ -10380,19 +10380,19 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_35.jpg</t>
+          <t>stimuli/dog/dog_30.jpg</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
           <t>hammer</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>house</t>
-        </is>
-      </c>
       <c r="K101" t="inlineStr">
         <is>
           <t>ball</t>
@@ -10400,7 +10400,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -10433,16 +10433,16 @@
         <v>10</v>
       </c>
       <c r="T101" t="n">
+        <v>4</v>
+      </c>
+      <c r="U101" t="n">
         <v>7</v>
-      </c>
-      <c r="U101" t="n">
-        <v>9</v>
       </c>
       <c r="V101" t="n">
         <v>1</v>
       </c>
       <c r="W101" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102">
@@ -10464,14 +10464,14 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
+          <t>stimuli/hammer/hammer_26.jpg</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
           <t>stimuli/house/house_05.jpg</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_22.jpg</t>
-        </is>
-      </c>
       <c r="G102" t="inlineStr">
         <is>
           <t>stimuli/glasses/glasses_06.jpg</t>
@@ -10484,12 +10484,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
           <t>house</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -10532,10 +10532,10 @@
         <v>11</v>
       </c>
       <c r="T102" t="n">
+        <v>7</v>
+      </c>
+      <c r="U102" t="n">
         <v>9</v>
-      </c>
-      <c r="U102" t="n">
-        <v>6</v>
       </c>
       <c r="V102" t="n">
         <v>18</v>
@@ -10563,14 +10563,14 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
+          <t>stimuli/house/house_05.jpg</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_30.jpg</t>
-        </is>
-      </c>
       <c r="G103" t="inlineStr">
         <is>
           <t>stimuli/guitar/guitar_32.jpg</t>
@@ -10578,19 +10578,19 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>stimuli/hammer/hammer_26.jpg</t>
+          <t>stimuli/chair/chair_16.jpg</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
+          <t>house</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
           <t>flower</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="K103" t="inlineStr">
         <is>
           <t>guitar</t>
@@ -10598,7 +10598,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>hammer</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -10631,16 +10631,16 @@
         <v>12</v>
       </c>
       <c r="T103" t="n">
+        <v>9</v>
+      </c>
+      <c r="U103" t="n">
         <v>6</v>
-      </c>
-      <c r="U103" t="n">
-        <v>5</v>
       </c>
       <c r="V103" t="n">
         <v>13</v>
       </c>
       <c r="W103" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="104">
@@ -10662,7 +10662,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_30.jpg</t>
+          <t>stimuli/flower/flower_22.jpg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -10682,7 +10682,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -10730,7 +10730,7 @@
         <v>13</v>
       </c>
       <c r="T104" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U104" t="n">
         <v>18</v>
@@ -10771,7 +10771,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_49.jpg</t>
+          <t>stimuli/jacket/jacket_35.jpg</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -10791,7 +10791,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -10835,7 +10835,7 @@
         <v>12</v>
       </c>
       <c r="V105" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="W105" t="n">
         <v>13</v>
